--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487556_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487556_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8868</v>
+        <v>9.4671</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9537</v>
+        <v>8.052899999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9331</v>
+        <v>1.4143</v>
       </c>
       <c r="G2" t="n">
         <v>6.7652</v>
@@ -610,13 +610,13 @@
         <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8784</v>
+        <v>0.7019</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5764</v>
+        <v>0.5228</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3021</v>
+        <v>0.1791</v>
       </c>
       <c r="V2" t="n">
         <v>1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5109</v>
+        <v>4.964</v>
       </c>
       <c r="E3" t="n">
-        <v>2.297</v>
+        <v>3.4986</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2139</v>
+        <v>1.4655</v>
       </c>
       <c r="G3" t="n">
         <v>6.0784</v>
@@ -688,13 +688,13 @@
         <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1145</v>
+        <v>0.5676</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3486</v>
+        <v>-0.147</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4631</v>
+        <v>0.7146</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1152</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. NIETO GONZALEZ</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1109</v>
+        <v>2.9407</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7764</v>
+        <v>2.3483</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6656</v>
+        <v>0.5924</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0288</v>
+        <v>-0.502</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3366</v>
+        <v>-1.644</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6922</v>
+        <v>1.142</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1486</v>
+        <v>1.0323</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6533</v>
+        <v>0.0527</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4954</v>
+        <v>0.9796</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1198</v>
+        <v>-1.5343</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6833</v>
+        <v>-1.6968</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8031</v>
+        <v>0.1624</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7111</v>
+        <v>0.3471</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6278</v>
+        <v>0.0994</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0833</v>
+        <v>0.2478</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8249</v>
+        <v>0.9412</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8249</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>J. NIETO GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8453</v>
+        <v>1.7141</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7608</v>
+        <v>3.1391</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08450000000000001</v>
+        <v>-1.425</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.502</v>
+        <v>2.0288</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.644</v>
+        <v>1.3366</v>
       </c>
       <c r="I5" t="n">
-        <v>1.142</v>
+        <v>0.6922</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0323</v>
+        <v>2.1486</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0527</v>
+        <v>0.6533</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9796</v>
+        <v>1.4954</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5343</v>
+        <v>-0.1198</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6968</v>
+        <v>0.6833</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1624</v>
+        <v>-0.8031</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1543</v>
+        <v>0.1958</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1543</v>
+        <v>0.1958</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7483</v>
+        <v>1.3143</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4882</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2601</v>
+        <v>0.3239</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9412</v>
+        <v>-1.8249</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2623</v>
+        <v>1.6209</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6346000000000001</v>
+        <v>0.0982</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8969</v>
+        <v>1.5227</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6193</v>
@@ -922,13 +922,13 @@
         <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1771</v>
+        <v>0.1814</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.891</v>
+        <v>-0.1582</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7139</v>
+        <v>0.3397</v>
       </c>
       <c r="V6" t="n">
         <v>0.8837</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1049</v>
+        <v>0.001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1231</v>
+        <v>-1.0135</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.228</v>
+        <v>1.0145</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1018</v>
+        <v>-0.9133</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4896</v>
+        <v>-1.257</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5914</v>
+        <v>0.3437</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8392</v>
+        <v>0.1544</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1804</v>
+        <v>0.5085</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0196</v>
+        <v>-0.3541</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7375</v>
+        <v>-1.0677</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3092</v>
+        <v>-1.7655</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5717</v>
+        <v>0.6978</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7419</v>
+        <v>1.9585</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8509</v>
+        <v>0.9143</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8667</v>
+        <v>0.5152</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0159</v>
+        <v>0.3991</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8825</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.396</v>
+        <v>-0.3098</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0784</v>
+        <v>-0.019</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3176</v>
+        <v>-0.2909</v>
       </c>
       <c r="G8" t="n">
         <v>-0.295</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.101</v>
+        <v>-0.0149</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1188</v>
+        <v>-0.0594</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>C. MONTERO MECA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5611</v>
+        <v>-0.6041</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3294</v>
+        <v>2.4935</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7683</v>
+        <v>-3.0976</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8197</v>
+        <v>1.6018</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8201</v>
+        <v>-0.9595</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0004</v>
+        <v>2.5614</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2988</v>
+        <v>2.3383</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3441</v>
+        <v>-0.2127</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0452</v>
+        <v>2.551</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4791</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.476</v>
+        <v>-0.7468</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.0104</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9256</v>
+        <v>0.0522</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9487</v>
+        <v>0.1553</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0231</v>
+        <v>-0.1031</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2754</v>
+        <v>-3.0415</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2754</v>
+        <v>-3.0415</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7469</v>
+        <v>-1.3844</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6011</v>
+        <v>-2.0458</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8541</v>
+        <v>0.6613</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9133</v>
+        <v>-0.8197</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.257</v>
+        <v>-1.8201</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3437</v>
+        <v>1.0004</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1544</v>
+        <v>-1.2988</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5085</v>
+        <v>-1.3441</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3541</v>
+        <v>0.0452</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0677</v>
+        <v>0.4791</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7655</v>
+        <v>-0.476</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6978</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9585</v>
+        <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1663</v>
+        <v>0.1023</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0723</v>
+        <v>0.2323</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2387</v>
+        <v>-0.13</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.2754</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. MONTERO MECA</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.988</v>
+        <v>-1.4024</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9225</v>
+        <v>-1.1743</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9105</v>
+        <v>-0.228</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6018</v>
+        <v>1.1018</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9595</v>
+        <v>-2.4896</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5614</v>
+        <v>3.5914</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3383</v>
+        <v>2.8392</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2127</v>
+        <v>-0.1804</v>
       </c>
       <c r="L11" t="n">
-        <v>2.551</v>
+        <v>3.0196</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-1.7375</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7468</v>
+        <v>-2.3092</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0104</v>
+        <v>0.5717</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7834</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7834</v>
+        <v>2.7419</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3318</v>
+        <v>0.5534</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4158</v>
+        <v>0.5693</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.0159</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.0415</v>
+        <v>-1.8825</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.0415</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.8193</v>
+        <v>17.0071</v>
       </c>
       <c r="E12" t="n">
-        <v>14.19</v>
+        <v>15.378</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6291</v>
+        <v>1.6292</v>
       </c>
       <c r="G12" t="n">
         <v>14.4267</v>
@@ -1366,7 +1366,7 @@
         <v>21.3798</v>
       </c>
       <c r="K12" t="n">
-        <v>4.0569</v>
+        <v>4.056900000000001</v>
       </c>
       <c r="L12" t="n">
         <v>17.3228</v>
@@ -1381,7 +1381,7 @@
         <v>2.8846</v>
       </c>
       <c r="P12" t="n">
-        <v>1.958400000000001</v>
+        <v>1.9584</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.7509</v>
@@ -1390,13 +1390,13 @@
         <v>13.7093</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5318</v>
+        <v>4.7196</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5321</v>
+        <v>2.7201</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9996</v>
+        <v>1.9998</v>
       </c>
       <c r="V12" t="n">
         <v>-4.098</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3744</v>
+        <v>2.8225</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6081</v>
+        <v>4.8128</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2337</v>
+        <v>-1.9903</v>
       </c>
       <c r="G13" t="n">
         <v>2.6178</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6351</v>
+        <v>-0.187</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.387</v>
+        <v>-0.1823</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2481</v>
+        <v>-0.0047</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.626</v>
+        <v>2.2031</v>
       </c>
       <c r="E14" t="n">
-        <v>0.915</v>
+        <v>1.222</v>
       </c>
       <c r="F14" t="n">
-        <v>0.711</v>
+        <v>0.9811</v>
       </c>
       <c r="G14" t="n">
         <v>0.7738</v>
@@ -1546,13 +1546,13 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4808</v>
+        <v>0.0963</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2088</v>
+        <v>0.0982</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.272</v>
+        <v>-0.0019</v>
       </c>
       <c r="V14" t="n">
         <v>0.9412</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9044</v>
+        <v>-0.259</v>
       </c>
       <c r="E15" t="n">
-        <v>1.275</v>
+        <v>0.4563</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3706</v>
+        <v>-0.7153</v>
       </c>
       <c r="G15" t="n">
         <v>-0.902</v>
@@ -1624,13 +1624,13 @@
         <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6265</v>
+        <v>0.4632</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9181</v>
+        <v>0.0994</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7085</v>
+        <v>0.3638</v>
       </c>
       <c r="V15" t="n">
         <v>1.159</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.4517</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3822</v>
+        <v>1.2799</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0017</v>
+        <v>-1.7316</v>
       </c>
       <c r="G16" t="n">
         <v>0.0414</v>
@@ -1702,13 +1702,13 @@
         <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2608</v>
+        <v>0.4286</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3546</v>
+        <v>0.2523</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.1763</v>
       </c>
       <c r="V16" t="n">
         <v>0.0576</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8369</v>
+        <v>-1.0905</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6188</v>
+        <v>0.3118</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4557</v>
+        <v>-1.4022</v>
       </c>
       <c r="G17" t="n">
         <v>0.9919</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.7702</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.09</v>
+        <v>-0.397</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4266</v>
+        <v>-0.3732</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3329</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9425</v>
+        <v>-1.346</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5591</v>
+        <v>-0.1497</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3834</v>
+        <v>-1.1963</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8714</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8545</v>
+        <v>-0.258</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.297</v>
+        <v>0.1123</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5575</v>
+        <v>-0.3704</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9658</v>
+        <v>-2.2081</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2854</v>
+        <v>-0.1831</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6804</v>
+        <v>-2.0251</v>
       </c>
       <c r="G19" t="n">
         <v>-4.0061</v>
@@ -1936,13 +1936,13 @@
         <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2131</v>
+        <v>-0.4555</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.5817</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4709</v>
+        <v>0.1262</v>
       </c>
       <c r="V19" t="n">
         <v>1.2742</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8554</v>
+        <v>-3.1937</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3116</v>
+        <v>-1.5162</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5439</v>
+        <v>-1.6775</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8257</v>
@@ -2014,13 +2014,13 @@
         <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>0.362</v>
+        <v>0.0237</v>
       </c>
       <c r="T20" t="n">
-        <v>0.207</v>
+        <v>0.0023</v>
       </c>
       <c r="U20" t="n">
-        <v>0.155</v>
+        <v>0.0213</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2781</v>
+        <v>-3.7618</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8288</v>
+        <v>-1.4195</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4492</v>
+        <v>-2.3423</v>
       </c>
       <c r="G21" t="n">
         <v>-3.5023</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5373</v>
+        <v>-1.021</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0098</v>
+        <v>-0.6005</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5274</v>
+        <v>-0.4205</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2178</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.2257</v>
+        <v>-7.8515</v>
       </c>
       <c r="E22" t="n">
         <v>-6.4433</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7824</v>
+        <v>-1.4082</v>
       </c>
       <c r="G22" t="n">
         <v>-5.7442</v>
@@ -2170,13 +2170,13 @@
         <v>1.7626</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5437</v>
+        <v>-1.1695</v>
       </c>
       <c r="T22" t="n">
         <v>-0.8028</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7409</v>
+        <v>-0.3667</v>
       </c>
       <c r="V22" t="n">
         <v>1.2166</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-15.8191</v>
+        <v>-15.1367</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.629099999999999</v>
+        <v>-1.629</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.19</v>
+        <v>-13.5077</v>
       </c>
       <c r="G23" t="n">
         <v>-14.4268</v>
@@ -2248,13 +2248,13 @@
         <v>11.7506</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.5318</v>
+        <v>-2.8494</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.9997</v>
+        <v>-1.9998</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.5319</v>
+        <v>-0.8498000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>4.0979</v>
